--- a/VPD PO download generator/VPD PO Download Spreadsheet v1.1.xlsx
+++ b/VPD PO download generator/VPD PO Download Spreadsheet v1.1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jwa25\source\repos\VPD PO download generator\VPD PO download generator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B500E9D-BF4F-46FA-867B-73DDE058453F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCBCE1BB-1E52-43B4-8EEF-EDDF72D15C9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E1429B42-6D56-496D-8C3D-7089E84A1C10}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="119">
   <si>
     <t>Type</t>
   </si>
@@ -154,25 +154,235 @@
     <t>BEBE</t>
   </si>
   <si>
-    <t>R-SO-5088990-1-1</t>
-  </si>
-  <si>
-    <t>R-SO-5088990-1-2</t>
-  </si>
-  <si>
-    <t>R-SO-5088990-2-1</t>
-  </si>
-  <si>
-    <t>R-SO-5088990-2-2</t>
-  </si>
-  <si>
-    <t>R-SO-5088990-3-1</t>
-  </si>
-  <si>
-    <t>R-SO-5088990-4-1</t>
-  </si>
-  <si>
-    <t>R-SO-5088990-4-2</t>
+    <t>R-SO-5114589-1.001-1</t>
+  </si>
+  <si>
+    <t>R-SO-5106483-1-1</t>
+  </si>
+  <si>
+    <t>R-SO-5109096-1-1</t>
+  </si>
+  <si>
+    <t>R-SO-5091872-1-1</t>
+  </si>
+  <si>
+    <t>R-SO-5091872-1-2</t>
+  </si>
+  <si>
+    <t>R-SO-5091872-1-3</t>
+  </si>
+  <si>
+    <t>R-SO-5091872-1-4</t>
+  </si>
+  <si>
+    <t>R-SO-5091872-1-5</t>
+  </si>
+  <si>
+    <t>R-SO-5091872-1-6</t>
+  </si>
+  <si>
+    <t>R-SO-5091872-1-7</t>
+  </si>
+  <si>
+    <t>R-SO-5091872-1-8</t>
+  </si>
+  <si>
+    <t>R-SO-5091872-1-9</t>
+  </si>
+  <si>
+    <t>R-SO-5091872-1-10</t>
+  </si>
+  <si>
+    <t>R-SO-5091872-1-11</t>
+  </si>
+  <si>
+    <t>R-SO-5091872-1-12</t>
+  </si>
+  <si>
+    <t>R-SO-5091872-1-13</t>
+  </si>
+  <si>
+    <t>R-SO-5091872-1-14</t>
+  </si>
+  <si>
+    <t>R-SO-5091872-1-15</t>
+  </si>
+  <si>
+    <t>R-SO-5091872-1-16</t>
+  </si>
+  <si>
+    <t>R-SO-5091872-1-17</t>
+  </si>
+  <si>
+    <t>R-SO-5091872-1-18</t>
+  </si>
+  <si>
+    <t>R-SO-5091872-1-19</t>
+  </si>
+  <si>
+    <t>R-SO-5091872-1-20</t>
+  </si>
+  <si>
+    <t>R-SO-5091872-2-1</t>
+  </si>
+  <si>
+    <t>R-SO-5091872-2-2</t>
+  </si>
+  <si>
+    <t>R-SO-5091872-2-3</t>
+  </si>
+  <si>
+    <t>R-SO-5091872-2-4</t>
+  </si>
+  <si>
+    <t>R-SO-5091872-2-5</t>
+  </si>
+  <si>
+    <t>R-SO-5091872-2-6</t>
+  </si>
+  <si>
+    <t>R-SO-5091872-2-7</t>
+  </si>
+  <si>
+    <t>R-SO-5091872-2-8</t>
+  </si>
+  <si>
+    <t>R-SO-5091872-2-9</t>
+  </si>
+  <si>
+    <t>R-SO-5091872-2-10</t>
+  </si>
+  <si>
+    <t>R-SO-5091872-2-11</t>
+  </si>
+  <si>
+    <t>R-SO-5091872-2-12</t>
+  </si>
+  <si>
+    <t>R-SO-5091872-2-13</t>
+  </si>
+  <si>
+    <t>R-SO-5091872-2-14</t>
+  </si>
+  <si>
+    <t>R-SO-5091872-2-15</t>
+  </si>
+  <si>
+    <t>R-SO-5091872-2-16</t>
+  </si>
+  <si>
+    <t>R-SO-5041841-4-1</t>
+  </si>
+  <si>
+    <t>R-SO-5041841-4-2</t>
+  </si>
+  <si>
+    <t>R-SO-5041841-4-3</t>
+  </si>
+  <si>
+    <t>R-SO-5041841-4-4</t>
+  </si>
+  <si>
+    <t>R-SO-5041841-5-1</t>
+  </si>
+  <si>
+    <t>R-SO-5041841-5-2</t>
+  </si>
+  <si>
+    <t>R-SO-5041841-5-3</t>
+  </si>
+  <si>
+    <t>R-SO-5041841-5-4</t>
+  </si>
+  <si>
+    <t>R-SO-5115104-1-1</t>
+  </si>
+  <si>
+    <t>R-SO-5115207-1-1</t>
+  </si>
+  <si>
+    <t>R-SO-5109286-5-1</t>
+  </si>
+  <si>
+    <t>R-SO-5113568-1-1</t>
+  </si>
+  <si>
+    <t>R-SO-5113568-2-1</t>
+  </si>
+  <si>
+    <t>R-SO-5113570-1-1</t>
+  </si>
+  <si>
+    <t>R-SO-5113570-2-1</t>
+  </si>
+  <si>
+    <t>R-SO-5113574-1-1</t>
+  </si>
+  <si>
+    <t>R-SO-5113574-2-1</t>
+  </si>
+  <si>
+    <t>R-SO-5113575-1-1</t>
+  </si>
+  <si>
+    <t>R-SO-5113575-2-1</t>
+  </si>
+  <si>
+    <t>R-SO-5113576-1-1</t>
+  </si>
+  <si>
+    <t>R-SO-5113576-2-1</t>
+  </si>
+  <si>
+    <t>R-SO-5109489-1-1</t>
+  </si>
+  <si>
+    <t>R-SO-5109489-1-2</t>
+  </si>
+  <si>
+    <t>R-SO-5107078-10-1</t>
+  </si>
+  <si>
+    <t>R-SO-5107078-11-1</t>
+  </si>
+  <si>
+    <t>R-SO-5114296-1-1</t>
+  </si>
+  <si>
+    <t>R-SO-5091315-4.001-1</t>
+  </si>
+  <si>
+    <t>R-SO-5106993-3-1</t>
+  </si>
+  <si>
+    <t>R-SO-5107701-9-1</t>
+  </si>
+  <si>
+    <t>R-SO-5108036-9-1</t>
+  </si>
+  <si>
+    <t>R-SO-5108127-6-1</t>
+  </si>
+  <si>
+    <t>R-SO-5106308-6-1</t>
+  </si>
+  <si>
+    <t>R-SO-5106308-7-1</t>
+  </si>
+  <si>
+    <t>R-SO-5108107-1-1</t>
+  </si>
+  <si>
+    <t>R-SO-5108563-1-1</t>
+  </si>
+  <si>
+    <t>R-SO-5109719-1-1</t>
+  </si>
+  <si>
+    <t>R-SO-5112437-2-1</t>
+  </si>
+  <si>
+    <t>R-SO-5109126-3-1</t>
   </si>
 </sst>
 </file>
@@ -577,11 +787,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E0080E7-F391-47B1-85B3-22F42F81BBBC}">
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:I127"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.5703125" customWidth="1"/>
-    <col min="2" max="2" width="20.42578125" customWidth="1"/>
+    <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -633,7 +843,7 @@
         <v>26</v>
       </c>
       <c r="E2" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F2" t="s">
         <v>11</v>
@@ -659,10 +869,10 @@
         <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E3" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F3" t="s">
         <v>11</v>
@@ -674,7 +884,7 @@
         <v>12</v>
       </c>
       <c r="I3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -682,16 +892,16 @@
         <v>44</v>
       </c>
       <c r="B4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C4" t="s">
         <v>19</v>
       </c>
       <c r="D4" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F4" t="s">
         <v>11</v>
@@ -703,7 +913,7 @@
         <v>12</v>
       </c>
       <c r="I4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -717,10 +927,10 @@
         <v>19</v>
       </c>
       <c r="D5" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F5" t="s">
         <v>11</v>
@@ -732,7 +942,7 @@
         <v>12</v>
       </c>
       <c r="I5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -746,10 +956,10 @@
         <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F6" t="s">
         <v>11</v>
@@ -761,7 +971,7 @@
         <v>12</v>
       </c>
       <c r="I6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -772,13 +982,13 @@
         <v>31</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D7" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F7" t="s">
         <v>11</v>
@@ -790,7 +1000,7 @@
         <v>12</v>
       </c>
       <c r="I7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -801,152 +1011,2203 @@
         <v>31</v>
       </c>
       <c r="C8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H8" t="s">
+        <v>12</v>
+      </c>
+      <c r="I8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" t="s">
+        <v>35</v>
+      </c>
+      <c r="F9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H9" t="s">
+        <v>12</v>
+      </c>
+      <c r="I9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>50</v>
+      </c>
+      <c r="B10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H10" t="s">
+        <v>12</v>
+      </c>
+      <c r="I10" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>51</v>
+      </c>
+      <c r="B11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" t="s">
+        <v>35</v>
+      </c>
+      <c r="F11" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H11" t="s">
+        <v>12</v>
+      </c>
+      <c r="I11" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>52</v>
+      </c>
+      <c r="B12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" t="s">
+        <v>35</v>
+      </c>
+      <c r="F12" t="s">
+        <v>11</v>
+      </c>
+      <c r="G12" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H12" t="s">
+        <v>12</v>
+      </c>
+      <c r="I12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E13" t="s">
+        <v>35</v>
+      </c>
+      <c r="F13" t="s">
+        <v>11</v>
+      </c>
+      <c r="G13" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H13" t="s">
+        <v>12</v>
+      </c>
+      <c r="I13" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" t="s">
+        <v>35</v>
+      </c>
+      <c r="F14" t="s">
+        <v>11</v>
+      </c>
+      <c r="G14" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H14" t="s">
+        <v>12</v>
+      </c>
+      <c r="I14" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>55</v>
+      </c>
+      <c r="B15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" t="s">
+        <v>35</v>
+      </c>
+      <c r="F15" t="s">
+        <v>11</v>
+      </c>
+      <c r="G15" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H15" t="s">
+        <v>12</v>
+      </c>
+      <c r="I15" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>56</v>
+      </c>
+      <c r="B16" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" t="s">
+        <v>35</v>
+      </c>
+      <c r="F16" t="s">
+        <v>11</v>
+      </c>
+      <c r="G16" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H16" t="s">
+        <v>12</v>
+      </c>
+      <c r="I16" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>57</v>
+      </c>
+      <c r="B17" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" t="s">
+        <v>35</v>
+      </c>
+      <c r="F17" t="s">
+        <v>11</v>
+      </c>
+      <c r="G17" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H17" t="s">
+        <v>12</v>
+      </c>
+      <c r="I17" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>58</v>
+      </c>
+      <c r="B18" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" t="s">
+        <v>19</v>
+      </c>
+      <c r="D18" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" t="s">
+        <v>35</v>
+      </c>
+      <c r="F18" t="s">
+        <v>11</v>
+      </c>
+      <c r="G18" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H18" t="s">
+        <v>12</v>
+      </c>
+      <c r="I18" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>59</v>
+      </c>
+      <c r="B19" t="s">
+        <v>31</v>
+      </c>
+      <c r="C19" t="s">
+        <v>19</v>
+      </c>
+      <c r="D19" t="s">
+        <v>20</v>
+      </c>
+      <c r="E19" t="s">
+        <v>35</v>
+      </c>
+      <c r="F19" t="s">
+        <v>11</v>
+      </c>
+      <c r="G19" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H19" t="s">
+        <v>12</v>
+      </c>
+      <c r="I19" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>60</v>
+      </c>
+      <c r="B20" t="s">
+        <v>31</v>
+      </c>
+      <c r="C20" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" t="s">
+        <v>35</v>
+      </c>
+      <c r="F20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G20" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H20" t="s">
+        <v>12</v>
+      </c>
+      <c r="I20" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>61</v>
+      </c>
+      <c r="B21" t="s">
+        <v>31</v>
+      </c>
+      <c r="C21" t="s">
+        <v>19</v>
+      </c>
+      <c r="D21" t="s">
+        <v>20</v>
+      </c>
+      <c r="E21" t="s">
+        <v>35</v>
+      </c>
+      <c r="F21" t="s">
+        <v>11</v>
+      </c>
+      <c r="G21" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H21" t="s">
+        <v>12</v>
+      </c>
+      <c r="I21" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>62</v>
+      </c>
+      <c r="B22" t="s">
+        <v>31</v>
+      </c>
+      <c r="C22" t="s">
+        <v>19</v>
+      </c>
+      <c r="D22" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" t="s">
+        <v>35</v>
+      </c>
+      <c r="F22" t="s">
+        <v>11</v>
+      </c>
+      <c r="G22" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H22" t="s">
+        <v>12</v>
+      </c>
+      <c r="I22" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>63</v>
+      </c>
+      <c r="B23" t="s">
+        <v>31</v>
+      </c>
+      <c r="C23" t="s">
+        <v>19</v>
+      </c>
+      <c r="D23" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" t="s">
+        <v>35</v>
+      </c>
+      <c r="F23" t="s">
+        <v>11</v>
+      </c>
+      <c r="G23" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H23" t="s">
+        <v>12</v>
+      </c>
+      <c r="I23" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>64</v>
+      </c>
+      <c r="B24" t="s">
+        <v>31</v>
+      </c>
+      <c r="C24" t="s">
+        <v>19</v>
+      </c>
+      <c r="D24" t="s">
+        <v>20</v>
+      </c>
+      <c r="E24" t="s">
+        <v>35</v>
+      </c>
+      <c r="F24" t="s">
+        <v>11</v>
+      </c>
+      <c r="G24" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H24" t="s">
+        <v>12</v>
+      </c>
+      <c r="I24" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>65</v>
+      </c>
+      <c r="B25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C25" t="s">
+        <v>19</v>
+      </c>
+      <c r="D25" t="s">
+        <v>20</v>
+      </c>
+      <c r="E25" t="s">
+        <v>35</v>
+      </c>
+      <c r="F25" t="s">
+        <v>11</v>
+      </c>
+      <c r="G25" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H25" t="s">
+        <v>12</v>
+      </c>
+      <c r="I25" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>66</v>
+      </c>
+      <c r="B26" t="s">
+        <v>31</v>
+      </c>
+      <c r="C26" t="s">
+        <v>19</v>
+      </c>
+      <c r="D26" t="s">
+        <v>20</v>
+      </c>
+      <c r="E26" t="s">
+        <v>35</v>
+      </c>
+      <c r="F26" t="s">
+        <v>11</v>
+      </c>
+      <c r="G26" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H26" t="s">
+        <v>12</v>
+      </c>
+      <c r="I26" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>67</v>
+      </c>
+      <c r="B27" t="s">
+        <v>31</v>
+      </c>
+      <c r="C27" t="s">
+        <v>19</v>
+      </c>
+      <c r="D27" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" t="s">
+        <v>35</v>
+      </c>
+      <c r="F27" t="s">
+        <v>11</v>
+      </c>
+      <c r="G27" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H27" t="s">
+        <v>12</v>
+      </c>
+      <c r="I27" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>68</v>
+      </c>
+      <c r="B28" t="s">
+        <v>31</v>
+      </c>
+      <c r="C28" t="s">
+        <v>19</v>
+      </c>
+      <c r="D28" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" t="s">
+        <v>35</v>
+      </c>
+      <c r="F28" t="s">
+        <v>11</v>
+      </c>
+      <c r="G28" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H28" t="s">
+        <v>12</v>
+      </c>
+      <c r="I28" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>69</v>
+      </c>
+      <c r="B29" t="s">
+        <v>31</v>
+      </c>
+      <c r="C29" t="s">
+        <v>19</v>
+      </c>
+      <c r="D29" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" t="s">
+        <v>35</v>
+      </c>
+      <c r="F29" t="s">
+        <v>11</v>
+      </c>
+      <c r="G29" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H29" t="s">
+        <v>12</v>
+      </c>
+      <c r="I29" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>70</v>
+      </c>
+      <c r="B30" t="s">
+        <v>31</v>
+      </c>
+      <c r="C30" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" t="s">
+        <v>35</v>
+      </c>
+      <c r="F30" t="s">
+        <v>11</v>
+      </c>
+      <c r="G30" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H30" t="s">
+        <v>12</v>
+      </c>
+      <c r="I30" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>71</v>
+      </c>
+      <c r="B31" t="s">
+        <v>31</v>
+      </c>
+      <c r="C31" t="s">
+        <v>19</v>
+      </c>
+      <c r="D31" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" t="s">
+        <v>35</v>
+      </c>
+      <c r="F31" t="s">
+        <v>11</v>
+      </c>
+      <c r="G31" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H31" t="s">
+        <v>12</v>
+      </c>
+      <c r="I31" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>72</v>
+      </c>
+      <c r="B32" t="s">
+        <v>31</v>
+      </c>
+      <c r="C32" t="s">
+        <v>19</v>
+      </c>
+      <c r="D32" t="s">
+        <v>20</v>
+      </c>
+      <c r="E32" t="s">
+        <v>35</v>
+      </c>
+      <c r="F32" t="s">
+        <v>11</v>
+      </c>
+      <c r="G32" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H32" t="s">
+        <v>12</v>
+      </c>
+      <c r="I32" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>73</v>
+      </c>
+      <c r="B33" t="s">
+        <v>31</v>
+      </c>
+      <c r="C33" t="s">
+        <v>19</v>
+      </c>
+      <c r="D33" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" t="s">
+        <v>35</v>
+      </c>
+      <c r="F33" t="s">
+        <v>11</v>
+      </c>
+      <c r="G33" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H33" t="s">
+        <v>12</v>
+      </c>
+      <c r="I33" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>74</v>
+      </c>
+      <c r="B34" t="s">
+        <v>31</v>
+      </c>
+      <c r="C34" t="s">
+        <v>19</v>
+      </c>
+      <c r="D34" t="s">
+        <v>20</v>
+      </c>
+      <c r="E34" t="s">
+        <v>35</v>
+      </c>
+      <c r="F34" t="s">
+        <v>11</v>
+      </c>
+      <c r="G34" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H34" t="s">
+        <v>12</v>
+      </c>
+      <c r="I34" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>75</v>
+      </c>
+      <c r="B35" t="s">
+        <v>31</v>
+      </c>
+      <c r="C35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D35" t="s">
+        <v>20</v>
+      </c>
+      <c r="E35" t="s">
+        <v>35</v>
+      </c>
+      <c r="F35" t="s">
+        <v>11</v>
+      </c>
+      <c r="G35" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H35" t="s">
+        <v>12</v>
+      </c>
+      <c r="I35" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>76</v>
+      </c>
+      <c r="B36" t="s">
+        <v>31</v>
+      </c>
+      <c r="C36" t="s">
+        <v>19</v>
+      </c>
+      <c r="D36" t="s">
+        <v>20</v>
+      </c>
+      <c r="E36" t="s">
+        <v>35</v>
+      </c>
+      <c r="F36" t="s">
+        <v>11</v>
+      </c>
+      <c r="G36" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H36" t="s">
+        <v>12</v>
+      </c>
+      <c r="I36" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>77</v>
+      </c>
+      <c r="B37" t="s">
+        <v>31</v>
+      </c>
+      <c r="C37" t="s">
+        <v>19</v>
+      </c>
+      <c r="D37" t="s">
+        <v>20</v>
+      </c>
+      <c r="E37" t="s">
+        <v>35</v>
+      </c>
+      <c r="F37" t="s">
+        <v>11</v>
+      </c>
+      <c r="G37" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H37" t="s">
+        <v>12</v>
+      </c>
+      <c r="I37" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>78</v>
+      </c>
+      <c r="B38" t="s">
+        <v>31</v>
+      </c>
+      <c r="C38" t="s">
+        <v>19</v>
+      </c>
+      <c r="D38" t="s">
+        <v>20</v>
+      </c>
+      <c r="E38" t="s">
+        <v>35</v>
+      </c>
+      <c r="F38" t="s">
+        <v>11</v>
+      </c>
+      <c r="G38" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H38" t="s">
+        <v>12</v>
+      </c>
+      <c r="I38" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>79</v>
+      </c>
+      <c r="B39" t="s">
+        <v>31</v>
+      </c>
+      <c r="C39" t="s">
+        <v>19</v>
+      </c>
+      <c r="D39" t="s">
+        <v>20</v>
+      </c>
+      <c r="E39" t="s">
+        <v>35</v>
+      </c>
+      <c r="F39" t="s">
+        <v>11</v>
+      </c>
+      <c r="G39" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H39" t="s">
+        <v>12</v>
+      </c>
+      <c r="I39" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>80</v>
+      </c>
+      <c r="B40" t="s">
+        <v>31</v>
+      </c>
+      <c r="C40" t="s">
+        <v>19</v>
+      </c>
+      <c r="D40" t="s">
+        <v>20</v>
+      </c>
+      <c r="E40" t="s">
+        <v>35</v>
+      </c>
+      <c r="F40" t="s">
+        <v>11</v>
+      </c>
+      <c r="G40" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H40" t="s">
+        <v>12</v>
+      </c>
+      <c r="I40" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>81</v>
+      </c>
+      <c r="B41" t="s">
+        <v>31</v>
+      </c>
+      <c r="C41" t="s">
+        <v>19</v>
+      </c>
+      <c r="D41" t="s">
+        <v>20</v>
+      </c>
+      <c r="E41" t="s">
+        <v>34</v>
+      </c>
+      <c r="F41" t="s">
+        <v>11</v>
+      </c>
+      <c r="G41" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H41" t="s">
+        <v>12</v>
+      </c>
+      <c r="I41" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>82</v>
+      </c>
+      <c r="B42" t="s">
+        <v>31</v>
+      </c>
+      <c r="C42" t="s">
+        <v>19</v>
+      </c>
+      <c r="D42" t="s">
+        <v>20</v>
+      </c>
+      <c r="E42" t="s">
+        <v>34</v>
+      </c>
+      <c r="F42" t="s">
+        <v>11</v>
+      </c>
+      <c r="G42" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H42" t="s">
+        <v>12</v>
+      </c>
+      <c r="I42" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>83</v>
+      </c>
+      <c r="B43" t="s">
+        <v>31</v>
+      </c>
+      <c r="C43" t="s">
+        <v>19</v>
+      </c>
+      <c r="D43" t="s">
+        <v>20</v>
+      </c>
+      <c r="E43" t="s">
+        <v>34</v>
+      </c>
+      <c r="F43" t="s">
+        <v>11</v>
+      </c>
+      <c r="G43" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H43" t="s">
+        <v>12</v>
+      </c>
+      <c r="I43" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>84</v>
+      </c>
+      <c r="B44" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" t="s">
+        <v>19</v>
+      </c>
+      <c r="D44" t="s">
+        <v>20</v>
+      </c>
+      <c r="E44" t="s">
+        <v>34</v>
+      </c>
+      <c r="F44" t="s">
+        <v>11</v>
+      </c>
+      <c r="G44" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H44" t="s">
+        <v>12</v>
+      </c>
+      <c r="I44" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>85</v>
+      </c>
+      <c r="B45" t="s">
+        <v>31</v>
+      </c>
+      <c r="C45" t="s">
+        <v>19</v>
+      </c>
+      <c r="D45" t="s">
+        <v>20</v>
+      </c>
+      <c r="E45" t="s">
+        <v>34</v>
+      </c>
+      <c r="F45" t="s">
+        <v>11</v>
+      </c>
+      <c r="G45" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H45" t="s">
+        <v>12</v>
+      </c>
+      <c r="I45" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>86</v>
+      </c>
+      <c r="B46" t="s">
+        <v>31</v>
+      </c>
+      <c r="C46" t="s">
+        <v>19</v>
+      </c>
+      <c r="D46" t="s">
+        <v>20</v>
+      </c>
+      <c r="E46" t="s">
+        <v>34</v>
+      </c>
+      <c r="F46" t="s">
+        <v>11</v>
+      </c>
+      <c r="G46" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H46" t="s">
+        <v>12</v>
+      </c>
+      <c r="I46" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>87</v>
+      </c>
+      <c r="B47" t="s">
+        <v>31</v>
+      </c>
+      <c r="C47" t="s">
+        <v>19</v>
+      </c>
+      <c r="D47" t="s">
+        <v>20</v>
+      </c>
+      <c r="E47" t="s">
+        <v>34</v>
+      </c>
+      <c r="F47" t="s">
+        <v>11</v>
+      </c>
+      <c r="G47" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H47" t="s">
+        <v>12</v>
+      </c>
+      <c r="I47" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>88</v>
+      </c>
+      <c r="B48" t="s">
+        <v>31</v>
+      </c>
+      <c r="C48" t="s">
+        <v>19</v>
+      </c>
+      <c r="D48" t="s">
+        <v>20</v>
+      </c>
+      <c r="E48" t="s">
+        <v>34</v>
+      </c>
+      <c r="F48" t="s">
+        <v>11</v>
+      </c>
+      <c r="G48" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H48" t="s">
+        <v>12</v>
+      </c>
+      <c r="I48" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>89</v>
+      </c>
+      <c r="B49" t="s">
+        <v>32</v>
+      </c>
+      <c r="C49" t="s">
+        <v>19</v>
+      </c>
+      <c r="D49" t="s">
         <v>26</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E49" t="s">
+        <v>41</v>
+      </c>
+      <c r="F49" t="s">
+        <v>11</v>
+      </c>
+      <c r="G49" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H49" t="s">
+        <v>12</v>
+      </c>
+      <c r="I49" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>90</v>
+      </c>
+      <c r="B50" t="s">
+        <v>32</v>
+      </c>
+      <c r="C50" t="s">
+        <v>19</v>
+      </c>
+      <c r="D50" t="s">
+        <v>26</v>
+      </c>
+      <c r="E50" t="s">
+        <v>39</v>
+      </c>
+      <c r="F50" t="s">
+        <v>11</v>
+      </c>
+      <c r="G50" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H50" t="s">
+        <v>12</v>
+      </c>
+      <c r="I50" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>91</v>
+      </c>
+      <c r="B51" t="s">
+        <v>31</v>
+      </c>
+      <c r="C51" t="s">
+        <v>19</v>
+      </c>
+      <c r="D51" t="s">
+        <v>26</v>
+      </c>
+      <c r="E51" t="s">
         <v>34</v>
       </c>
-      <c r="F8" t="s">
-        <v>11</v>
-      </c>
-      <c r="G8" s="4">
-        <v>46007</v>
-      </c>
-      <c r="H8" t="s">
-        <v>12</v>
-      </c>
-      <c r="I8" t="s">
+      <c r="F51" t="s">
+        <v>11</v>
+      </c>
+      <c r="G51" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H51" t="s">
+        <v>12</v>
+      </c>
+      <c r="I51" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G9" s="4"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G10" s="4"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G11" s="4"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G12" s="4"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G13" s="4"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G14" s="4"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G15" s="4"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G16" s="4"/>
-    </row>
-    <row r="17" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G17" s="4"/>
-    </row>
-    <row r="18" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G18" s="4"/>
-    </row>
-    <row r="19" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G19" s="4"/>
-    </row>
-    <row r="20" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G20" s="4"/>
-    </row>
-    <row r="21" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G21" s="4"/>
-    </row>
-    <row r="22" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G22" s="4"/>
-    </row>
-    <row r="23" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G23" s="4"/>
-    </row>
-    <row r="24" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G24" s="4"/>
-    </row>
-    <row r="25" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G25" s="4"/>
-    </row>
-    <row r="26" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G26" s="4"/>
-    </row>
-    <row r="27" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G27" s="4"/>
-    </row>
-    <row r="28" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G28" s="4"/>
-    </row>
-    <row r="29" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G29" s="4"/>
-    </row>
-    <row r="30" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G30" s="4"/>
-    </row>
-    <row r="31" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G31" s="4"/>
-    </row>
-    <row r="32" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G32" s="4"/>
-    </row>
-    <row r="33" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G33" s="4"/>
-    </row>
-    <row r="34" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G34" s="4"/>
-    </row>
-    <row r="35" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G35" s="4"/>
-    </row>
-    <row r="36" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G36" s="4"/>
-    </row>
-    <row r="37" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G37" s="4"/>
-    </row>
-    <row r="38" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G38" s="4"/>
-    </row>
-    <row r="39" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G39" s="4"/>
-    </row>
-    <row r="40" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G40" s="4"/>
-    </row>
-    <row r="41" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G41" s="4"/>
-    </row>
-    <row r="42" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G42" s="4"/>
-    </row>
-    <row r="43" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G43" s="4"/>
-    </row>
-    <row r="44" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G44" s="4"/>
-    </row>
-    <row r="45" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G45" s="4"/>
-    </row>
-    <row r="46" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G46" s="4"/>
-    </row>
-    <row r="47" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G47" s="4"/>
-    </row>
-    <row r="48" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G48" s="4"/>
-    </row>
-    <row r="49" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G49" s="4"/>
-    </row>
-    <row r="50" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G50" s="4"/>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>92</v>
+      </c>
+      <c r="B52" t="s">
+        <v>31</v>
+      </c>
+      <c r="C52" t="s">
+        <v>19</v>
+      </c>
+      <c r="D52" t="s">
+        <v>20</v>
+      </c>
+      <c r="E52" t="s">
+        <v>39</v>
+      </c>
+      <c r="F52" t="s">
+        <v>11</v>
+      </c>
+      <c r="G52" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H52" t="s">
+        <v>12</v>
+      </c>
+      <c r="I52" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>93</v>
+      </c>
+      <c r="B53" t="s">
+        <v>31</v>
+      </c>
+      <c r="C53" t="s">
+        <v>19</v>
+      </c>
+      <c r="D53" t="s">
+        <v>20</v>
+      </c>
+      <c r="E53" t="s">
+        <v>39</v>
+      </c>
+      <c r="F53" t="s">
+        <v>11</v>
+      </c>
+      <c r="G53" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H53" t="s">
+        <v>12</v>
+      </c>
+      <c r="I53" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>94</v>
+      </c>
+      <c r="B54" t="s">
+        <v>31</v>
+      </c>
+      <c r="C54" t="s">
+        <v>19</v>
+      </c>
+      <c r="D54" t="s">
+        <v>20</v>
+      </c>
+      <c r="E54" t="s">
+        <v>39</v>
+      </c>
+      <c r="F54" t="s">
+        <v>11</v>
+      </c>
+      <c r="G54" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H54" t="s">
+        <v>12</v>
+      </c>
+      <c r="I54" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>95</v>
+      </c>
+      <c r="B55" t="s">
+        <v>31</v>
+      </c>
+      <c r="C55" t="s">
+        <v>19</v>
+      </c>
+      <c r="D55" t="s">
+        <v>20</v>
+      </c>
+      <c r="E55" t="s">
+        <v>39</v>
+      </c>
+      <c r="F55" t="s">
+        <v>11</v>
+      </c>
+      <c r="G55" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H55" t="s">
+        <v>12</v>
+      </c>
+      <c r="I55" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>96</v>
+      </c>
+      <c r="B56" t="s">
+        <v>31</v>
+      </c>
+      <c r="C56" t="s">
+        <v>19</v>
+      </c>
+      <c r="D56" t="s">
+        <v>20</v>
+      </c>
+      <c r="E56" t="s">
+        <v>39</v>
+      </c>
+      <c r="F56" t="s">
+        <v>11</v>
+      </c>
+      <c r="G56" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H56" t="s">
+        <v>12</v>
+      </c>
+      <c r="I56" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>97</v>
+      </c>
+      <c r="B57" t="s">
+        <v>31</v>
+      </c>
+      <c r="C57" t="s">
+        <v>19</v>
+      </c>
+      <c r="D57" t="s">
+        <v>20</v>
+      </c>
+      <c r="E57" t="s">
+        <v>39</v>
+      </c>
+      <c r="F57" t="s">
+        <v>11</v>
+      </c>
+      <c r="G57" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H57" t="s">
+        <v>12</v>
+      </c>
+      <c r="I57" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>98</v>
+      </c>
+      <c r="B58" t="s">
+        <v>31</v>
+      </c>
+      <c r="C58" t="s">
+        <v>19</v>
+      </c>
+      <c r="D58" t="s">
+        <v>20</v>
+      </c>
+      <c r="E58" t="s">
+        <v>39</v>
+      </c>
+      <c r="F58" t="s">
+        <v>11</v>
+      </c>
+      <c r="G58" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H58" t="s">
+        <v>12</v>
+      </c>
+      <c r="I58" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>99</v>
+      </c>
+      <c r="B59" t="s">
+        <v>31</v>
+      </c>
+      <c r="C59" t="s">
+        <v>19</v>
+      </c>
+      <c r="D59" t="s">
+        <v>20</v>
+      </c>
+      <c r="E59" t="s">
+        <v>39</v>
+      </c>
+      <c r="F59" t="s">
+        <v>11</v>
+      </c>
+      <c r="G59" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H59" t="s">
+        <v>12</v>
+      </c>
+      <c r="I59" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>100</v>
+      </c>
+      <c r="B60" t="s">
+        <v>31</v>
+      </c>
+      <c r="C60" t="s">
+        <v>19</v>
+      </c>
+      <c r="D60" t="s">
+        <v>20</v>
+      </c>
+      <c r="E60" t="s">
+        <v>39</v>
+      </c>
+      <c r="F60" t="s">
+        <v>11</v>
+      </c>
+      <c r="G60" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H60" t="s">
+        <v>12</v>
+      </c>
+      <c r="I60" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>101</v>
+      </c>
+      <c r="B61" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" t="s">
+        <v>19</v>
+      </c>
+      <c r="D61" t="s">
+        <v>20</v>
+      </c>
+      <c r="E61" t="s">
+        <v>39</v>
+      </c>
+      <c r="F61" t="s">
+        <v>11</v>
+      </c>
+      <c r="G61" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H61" t="s">
+        <v>12</v>
+      </c>
+      <c r="I61" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>102</v>
+      </c>
+      <c r="B62" t="s">
+        <v>31</v>
+      </c>
+      <c r="C62" t="s">
+        <v>19</v>
+      </c>
+      <c r="D62" t="s">
+        <v>20</v>
+      </c>
+      <c r="E62" t="s">
+        <v>39</v>
+      </c>
+      <c r="F62" t="s">
+        <v>11</v>
+      </c>
+      <c r="G62" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H62" t="s">
+        <v>12</v>
+      </c>
+      <c r="I62" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>103</v>
+      </c>
+      <c r="B63" t="s">
+        <v>31</v>
+      </c>
+      <c r="C63" t="s">
+        <v>19</v>
+      </c>
+      <c r="D63" t="s">
+        <v>20</v>
+      </c>
+      <c r="E63" t="s">
+        <v>39</v>
+      </c>
+      <c r="F63" t="s">
+        <v>11</v>
+      </c>
+      <c r="G63" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H63" t="s">
+        <v>12</v>
+      </c>
+      <c r="I63" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>104</v>
+      </c>
+      <c r="B64" t="s">
+        <v>31</v>
+      </c>
+      <c r="C64" t="s">
+        <v>19</v>
+      </c>
+      <c r="D64" t="s">
+        <v>20</v>
+      </c>
+      <c r="E64" t="s">
+        <v>34</v>
+      </c>
+      <c r="F64" t="s">
+        <v>11</v>
+      </c>
+      <c r="G64" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H64" t="s">
+        <v>12</v>
+      </c>
+      <c r="I64" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>105</v>
+      </c>
+      <c r="B65" t="s">
+        <v>31</v>
+      </c>
+      <c r="C65" t="s">
+        <v>19</v>
+      </c>
+      <c r="D65" t="s">
+        <v>20</v>
+      </c>
+      <c r="E65" t="s">
+        <v>34</v>
+      </c>
+      <c r="F65" t="s">
+        <v>11</v>
+      </c>
+      <c r="G65" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H65" t="s">
+        <v>12</v>
+      </c>
+      <c r="I65" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>106</v>
+      </c>
+      <c r="B66" t="s">
+        <v>31</v>
+      </c>
+      <c r="C66" t="s">
+        <v>19</v>
+      </c>
+      <c r="D66" t="s">
+        <v>27</v>
+      </c>
+      <c r="E66" t="s">
+        <v>39</v>
+      </c>
+      <c r="F66" t="s">
+        <v>11</v>
+      </c>
+      <c r="G66" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H66" t="s">
+        <v>12</v>
+      </c>
+      <c r="I66" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>107</v>
+      </c>
+      <c r="B67" t="s">
+        <v>31</v>
+      </c>
+      <c r="C67" t="s">
+        <v>19</v>
+      </c>
+      <c r="D67" t="s">
+        <v>26</v>
+      </c>
+      <c r="E67" t="s">
+        <v>34</v>
+      </c>
+      <c r="F67" t="s">
+        <v>11</v>
+      </c>
+      <c r="G67" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H67" t="s">
+        <v>12</v>
+      </c>
+      <c r="I67" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>108</v>
+      </c>
+      <c r="B68" t="s">
+        <v>31</v>
+      </c>
+      <c r="C68" t="s">
+        <v>19</v>
+      </c>
+      <c r="D68" t="s">
+        <v>26</v>
+      </c>
+      <c r="E68" t="s">
+        <v>34</v>
+      </c>
+      <c r="F68" t="s">
+        <v>11</v>
+      </c>
+      <c r="G68" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H68" t="s">
+        <v>12</v>
+      </c>
+      <c r="I68" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>109</v>
+      </c>
+      <c r="B69" t="s">
+        <v>31</v>
+      </c>
+      <c r="C69" t="s">
+        <v>19</v>
+      </c>
+      <c r="D69" t="s">
+        <v>26</v>
+      </c>
+      <c r="E69" t="s">
+        <v>34</v>
+      </c>
+      <c r="F69" t="s">
+        <v>11</v>
+      </c>
+      <c r="G69" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H69" t="s">
+        <v>12</v>
+      </c>
+      <c r="I69" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>110</v>
+      </c>
+      <c r="B70" t="s">
+        <v>31</v>
+      </c>
+      <c r="C70" t="s">
+        <v>19</v>
+      </c>
+      <c r="D70" t="s">
+        <v>26</v>
+      </c>
+      <c r="E70" t="s">
+        <v>34</v>
+      </c>
+      <c r="F70" t="s">
+        <v>11</v>
+      </c>
+      <c r="G70" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H70" t="s">
+        <v>12</v>
+      </c>
+      <c r="I70" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>111</v>
+      </c>
+      <c r="B71" t="s">
+        <v>31</v>
+      </c>
+      <c r="C71" t="s">
+        <v>19</v>
+      </c>
+      <c r="D71" t="s">
+        <v>26</v>
+      </c>
+      <c r="E71" t="s">
+        <v>34</v>
+      </c>
+      <c r="F71" t="s">
+        <v>11</v>
+      </c>
+      <c r="G71" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H71" t="s">
+        <v>12</v>
+      </c>
+      <c r="I71" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>112</v>
+      </c>
+      <c r="B72" t="s">
+        <v>31</v>
+      </c>
+      <c r="C72" t="s">
+        <v>19</v>
+      </c>
+      <c r="D72" t="s">
+        <v>26</v>
+      </c>
+      <c r="E72" t="s">
+        <v>34</v>
+      </c>
+      <c r="F72" t="s">
+        <v>11</v>
+      </c>
+      <c r="G72" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H72" t="s">
+        <v>12</v>
+      </c>
+      <c r="I72" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>113</v>
+      </c>
+      <c r="B73" t="s">
+        <v>31</v>
+      </c>
+      <c r="C73" t="s">
+        <v>19</v>
+      </c>
+      <c r="D73" t="s">
+        <v>26</v>
+      </c>
+      <c r="E73" t="s">
+        <v>34</v>
+      </c>
+      <c r="F73" t="s">
+        <v>11</v>
+      </c>
+      <c r="G73" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H73" t="s">
+        <v>12</v>
+      </c>
+      <c r="I73" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>114</v>
+      </c>
+      <c r="B74" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" t="s">
+        <v>19</v>
+      </c>
+      <c r="D74" t="s">
+        <v>26</v>
+      </c>
+      <c r="E74" t="s">
+        <v>34</v>
+      </c>
+      <c r="F74" t="s">
+        <v>11</v>
+      </c>
+      <c r="G74" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H74" t="s">
+        <v>12</v>
+      </c>
+      <c r="I74" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>115</v>
+      </c>
+      <c r="B75" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" t="s">
+        <v>19</v>
+      </c>
+      <c r="D75" t="s">
+        <v>26</v>
+      </c>
+      <c r="E75" t="s">
+        <v>34</v>
+      </c>
+      <c r="F75" t="s">
+        <v>11</v>
+      </c>
+      <c r="G75" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H75" t="s">
+        <v>12</v>
+      </c>
+      <c r="I75" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>116</v>
+      </c>
+      <c r="B76" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" t="s">
+        <v>19</v>
+      </c>
+      <c r="D76" t="s">
+        <v>26</v>
+      </c>
+      <c r="E76" t="s">
+        <v>34</v>
+      </c>
+      <c r="F76" t="s">
+        <v>11</v>
+      </c>
+      <c r="G76" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H76" t="s">
+        <v>12</v>
+      </c>
+      <c r="I76" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>117</v>
+      </c>
+      <c r="B77" t="s">
+        <v>33</v>
+      </c>
+      <c r="C77" t="s">
+        <v>19</v>
+      </c>
+      <c r="D77" t="s">
+        <v>26</v>
+      </c>
+      <c r="E77" t="s">
+        <v>34</v>
+      </c>
+      <c r="F77" t="s">
+        <v>11</v>
+      </c>
+      <c r="G77" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H77" t="s">
+        <v>12</v>
+      </c>
+      <c r="I77" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>118</v>
+      </c>
+      <c r="B78" t="s">
+        <v>31</v>
+      </c>
+      <c r="C78" t="s">
+        <v>19</v>
+      </c>
+      <c r="D78" t="s">
+        <v>20</v>
+      </c>
+      <c r="E78" t="s">
+        <v>39</v>
+      </c>
+      <c r="F78" t="s">
+        <v>11</v>
+      </c>
+      <c r="G78" s="4">
+        <v>46007</v>
+      </c>
+      <c r="H78" t="s">
+        <v>12</v>
+      </c>
+      <c r="I78" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G79" s="4"/>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G80" s="4"/>
+    </row>
+    <row r="81" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G81" s="4"/>
+    </row>
+    <row r="82" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G82" s="4"/>
+    </row>
+    <row r="83" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G83" s="4"/>
+    </row>
+    <row r="84" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G84" s="4"/>
+    </row>
+    <row r="85" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G85" s="4"/>
+    </row>
+    <row r="86" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G86" s="4"/>
+    </row>
+    <row r="87" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G87" s="4"/>
+    </row>
+    <row r="88" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G88" s="4"/>
+    </row>
+    <row r="89" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G89" s="4"/>
+    </row>
+    <row r="90" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G90" s="4"/>
+    </row>
+    <row r="91" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G91" s="4"/>
+    </row>
+    <row r="92" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G92" s="4"/>
+    </row>
+    <row r="93" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G93" s="4"/>
+    </row>
+    <row r="94" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G94" s="4"/>
+    </row>
+    <row r="95" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G95" s="4"/>
+    </row>
+    <row r="96" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G96" s="4"/>
+    </row>
+    <row r="97" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G97" s="4"/>
+    </row>
+    <row r="98" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G98" s="4"/>
+    </row>
+    <row r="99" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G99" s="4"/>
+    </row>
+    <row r="100" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G100" s="4"/>
+    </row>
+    <row r="101" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G101" s="4"/>
+    </row>
+    <row r="102" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G102" s="4"/>
+    </row>
+    <row r="103" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G103" s="4"/>
+    </row>
+    <row r="104" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G104" s="4"/>
+    </row>
+    <row r="105" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G105" s="4"/>
+    </row>
+    <row r="106" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G106" s="4"/>
+    </row>
+    <row r="107" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G107" s="4"/>
+    </row>
+    <row r="108" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G108" s="4"/>
+    </row>
+    <row r="109" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G109" s="4"/>
+    </row>
+    <row r="110" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G110" s="4"/>
+    </row>
+    <row r="111" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G111" s="4"/>
+    </row>
+    <row r="112" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G112" s="4"/>
+    </row>
+    <row r="113" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G113" s="4"/>
+    </row>
+    <row r="114" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G114" s="4"/>
+    </row>
+    <row r="115" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G115" s="4"/>
+    </row>
+    <row r="116" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G116" s="4"/>
+    </row>
+    <row r="117" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G117" s="4"/>
+    </row>
+    <row r="118" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G118" s="4"/>
+    </row>
+    <row r="119" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G119" s="4"/>
+    </row>
+    <row r="120" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G120" s="4"/>
+    </row>
+    <row r="121" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G121" s="4"/>
+    </row>
+    <row r="122" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G122" s="4"/>
+    </row>
+    <row r="123" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G123" s="4"/>
+    </row>
+    <row r="124" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G124" s="4"/>
+    </row>
+    <row r="125" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G125" s="4"/>
+    </row>
+    <row r="126" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G126" s="4"/>
+    </row>
+    <row r="127" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G127" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -959,31 +3220,31 @@
           <x14:formula1>
             <xm:f>Sheet2!$D$4:$D$20</xm:f>
           </x14:formula1>
-          <xm:sqref>E1:E1048576</xm:sqref>
+          <xm:sqref>E79:E1048576 E1</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{E8C068A2-6DE7-4E34-819E-6972AEA4C823}">
           <x14:formula1>
             <xm:f>Sheet2!$F$4:$F$67</xm:f>
           </x14:formula1>
-          <xm:sqref>C1 C9:C1048576</xm:sqref>
+          <xm:sqref>C1 C79:C1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{F9DC1F6E-6608-4806-AA11-2BE452CCA365}">
           <x14:formula1>
             <xm:f>Sheet2!$H$4:$H$67</xm:f>
           </x14:formula1>
-          <xm:sqref>D1 D9:D1048576</xm:sqref>
+          <xm:sqref>D1 D79:D1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{9744BA83-CC56-4834-8B3C-78067D3AFEDF}">
           <x14:formula1>
             <xm:f>Sheet2!$B$4:$B$8</xm:f>
           </x14:formula1>
-          <xm:sqref>B1:B1048576</xm:sqref>
+          <xm:sqref>B1 B79:B1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{4D24AA4F-7F7F-41B1-86AE-9303F6EFC15D}">
           <x14:formula1>
             <xm:f>Sheet2!$J$4:$J$5</xm:f>
           </x14:formula1>
-          <xm:sqref>I1:I1048576</xm:sqref>
+          <xm:sqref>I1 I52:I53 I79:I1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
